--- a/sheets/조재수대금교본/검수/천개의 바람이 되어.xlsx
+++ b/sheets/조재수대금교본/검수/천개의 바람이 되어.xlsx
@@ -2753,7 +2753,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∽</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -2832,11 +2832,7 @@
         </is>
       </c>
       <c r="G6" s="24"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -2883,8 +2879,7 @@
       <c r="C8" s="23"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E8" s="23"/>
@@ -2896,16 +2891,11 @@
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="I8" s="23"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="23"/>
     </row>
     <row r="9" ht="91.25" customHeight="true">
@@ -2947,8 +2937,7 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="E10" s="24"/>
@@ -2962,8 +2951,7 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="I10" s="24"/>
@@ -3069,11 +3057,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -3082,17 +3066,9 @@
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
     </row>
     <row r="15" ht="91.25" customHeight="true">

--- a/sheets/조재수대금교본/검수/천개의 바람이 되어.xlsx
+++ b/sheets/조재수대금교본/검수/천개의 바람이 되어.xlsx
@@ -2753,7 +2753,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">姑∽</t>
         </is>
       </c>
       <c r="G3" s="22"/>

--- a/sheets/조재수대금교본/검수/천개의 바람이 되어.xlsx
+++ b/sheets/조재수대금교본/검수/천개의 바람이 되어.xlsx
@@ -2705,22 +2705,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="57.14" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="63.76" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="63.76" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="63.76" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="63.76" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="63.76" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="63.76" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -2898,7 +2898,7 @@
       <c r="J8" s="21"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="63.76" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="63.76" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="63.76" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="63.76" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="63.76" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="63.76" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3071,7 +3071,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="63.76" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="63.76" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="63.76" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="63.76" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -3205,6 +3205,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
 </worksheet>
 </file>